--- a/samples/Sample_9_For_School_Management_Section_C_Class7.xlsx
+++ b/samples/Sample_9_For_School_Management_Section_C_Class7.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aarav Desai</t>
+          <t>Aarav Joshi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diya Verma</t>
+          <t>Diya Sharma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aarav Bhat</t>
+          <t>Arjun Iyer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meera Pai</t>
+          <t>Myra Rao</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pranav Verma</t>
+          <t>Yash Verma</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ishita Patel</t>
+          <t>Aadhya Sharma</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rohan Sharma</t>
+          <t>Rohan Naik</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Neha Naik</t>
+          <t>Meera Patel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Devansh Sharma</t>
+          <t>Krishna Nair</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Riya Prabhu</t>
+          <t>Diya Kumar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vihaan Nair</t>
+          <t>Vihaan Hegde</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pooja Joshi</t>
+          <t>Anjali Sharma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Krishna Naik</t>
+          <t>Akash Murthy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Divya Hegde</t>
+          <t>Nisha Sharma</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Akash Joshi</t>
+          <t>Siddharth Kumar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kavya Pai</t>
+          <t>Ananya Sharma</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nikhil Pai</t>
+          <t>Reyansh Reddy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nisha Joshi</t>
+          <t>Aadhya Gowda</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vikram Pai</t>
+          <t>Akash Bhat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ananya Desai</t>
+          <t>Ishita Pai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vivaan Verma</t>
+          <t>Arjun Murthy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Anjali Naik</t>
+          <t>Neha Shetty</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rohan Nair</t>
+          <t>Pranav Bhat</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kritika Joshi</t>
+          <t>Sara Desai</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pranav Pai</t>
+          <t>Reyansh Kulkarni</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kavya Iyer</t>
+          <t>Pooja Kulkarni</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rohan Patel</t>
+          <t>Akash Desai</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anjali Reddy</t>
+          <t>Pooja Shetty</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rohan Gowda</t>
+          <t>Aditya Kulkarni</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Priya Bhat</t>
+          <t>Ananya Iyer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1615,19 +1615,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E2" t="n">
         <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1646,25 +1646,33 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1673,28 +1681,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
         <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1704,26 +1708,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Perimeter &amp; Area</t>
+          <t>Ratio &amp; Proportion</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1735,28 +1739,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1766,26 +1766,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
+          <t>Simple Equations</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1797,28 +1797,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Perimeter &amp; Area</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1828,29 +1824,29 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Fractions &amp; Decimals</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Inconsistent results — strong in some tests, weak in others.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1859,24 +1855,28 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>38</v>
+      </c>
+      <c r="C10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" t="n">
         <v>41</v>
-      </c>
-      <c r="C10" t="n">
-        <v>44</v>
-      </c>
-      <c r="D10" t="n">
-        <v>43</v>
       </c>
       <c r="E10" t="n">
         <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ratio &amp; Proportion</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1886,26 +1886,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
+          <t>Simple Equations</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1917,29 +1917,29 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>29</v>
+      </c>
+      <c r="C12" t="n">
+        <v>29</v>
+      </c>
+      <c r="D12" t="n">
         <v>27</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>30</v>
       </c>
-      <c r="D12" t="n">
-        <v>32</v>
-      </c>
-      <c r="E12" t="n">
-        <v>32</v>
-      </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1948,24 +1948,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
         <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ratio &amp; Proportion</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1978,22 +1982,30 @@
         <v>18</v>
       </c>
       <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" t="n">
         <v>19</v>
       </c>
-      <c r="D14" t="n">
-        <v>16</v>
-      </c>
-      <c r="E14" t="n">
-        <v>17</v>
-      </c>
-      <c r="F14" t="n">
-        <v>18</v>
-      </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Perimeter &amp; Area</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Below expectations — recommend extra classes after school.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2002,29 +2014,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Serious concern — immediate intervention needed.</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2033,33 +2041,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Simple Equations</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Very low scores across the board, please involve parents.</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2071,23 +2071,23 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fractions &amp; Decimals</t>
+          <t>Lines &amp; Angles</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2099,33 +2099,25 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>44</v>
+      </c>
+      <c r="C18" t="n">
+        <v>42</v>
+      </c>
+      <c r="D18" t="n">
         <v>41</v>
       </c>
-      <c r="C18" t="n">
-        <v>38</v>
-      </c>
-      <c r="D18" t="n">
-        <v>42</v>
-      </c>
       <c r="E18" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Fractions &amp; Decimals</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Noticeable drop in performance, please check in at home.</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2134,29 +2126,29 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Fractions &amp; Decimals</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Unpredictable performance, may help to identify what's different on good days.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2165,29 +2157,25 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>42</v>
+      </c>
+      <c r="C20" t="n">
+        <v>42</v>
+      </c>
+      <c r="D20" t="n">
+        <v>37</v>
+      </c>
+      <c r="E20" t="n">
         <v>38</v>
       </c>
-      <c r="C20" t="n">
-        <v>41</v>
-      </c>
-      <c r="D20" t="n">
-        <v>40</v>
-      </c>
-      <c r="E20" t="n">
-        <v>42</v>
-      </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2196,26 +2184,26 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D21" t="n">
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
+          <t>Ratio &amp; Proportion</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2227,31 +2215,31 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>27</v>
+      </c>
+      <c r="C22" t="n">
+        <v>29</v>
+      </c>
+      <c r="D22" t="n">
         <v>30</v>
       </c>
-      <c r="C22" t="n">
-        <v>30</v>
-      </c>
-      <c r="D22" t="n">
-        <v>32</v>
-      </c>
       <c r="E22" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
+          <t>Fractions &amp; Decimals</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -2262,19 +2250,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C23" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2293,29 +2281,29 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E24" t="n">
         <v>14</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>17</v>
       </c>
-      <c r="F24" t="n">
-        <v>14</v>
-      </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2324,28 +2312,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Fractions &amp; Decimals</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2355,19 +2339,19 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>9</v>
+      </c>
+      <c r="C26" t="n">
+        <v>11</v>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
         <v>6</v>
       </c>
-      <c r="C26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" t="n">
-        <v>9</v>
-      </c>
-      <c r="E26" t="n">
-        <v>5</v>
-      </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2386,29 +2370,33 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Simple Equations</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Encouraging progress, on the right track now.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2417,26 +2405,26 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C28" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D28" t="n">
+        <v>43</v>
+      </c>
+      <c r="E28" t="n">
         <v>41</v>
       </c>
-      <c r="E28" t="n">
-        <v>40</v>
-      </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Simple Equations</t>
+          <t>Fractions &amp; Decimals</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -2448,28 +2436,24 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C29" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2479,19 +2463,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C30" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E30" t="n">
         <v>41</v>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2506,26 +2490,26 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C31" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F31" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Perimeter &amp; Area</t>
+          <t>Simple Equations</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -2609,28 +2593,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2" t="n">
         <v>68</v>
       </c>
-      <c r="F2" t="n">
-        <v>58</v>
-      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Heat</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -2640,16 +2620,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
         <v>61</v>
@@ -2657,16 +2637,8 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2675,24 +2647,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Heat</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -2702,26 +2678,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Motion &amp; Time</t>
+          <t>Nutrition in Plants</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2733,33 +2709,29 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Very low scores across the board, please involve parents.</t>
-        </is>
-      </c>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2768,29 +2740,33 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F7" t="n">
         <v>54</v>
       </c>
-      <c r="F7" t="n">
-        <v>50</v>
-      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Visible improvement — the extra effort is showing results.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2799,20 +2775,20 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>72</v>
+      </c>
+      <c r="C8" t="n">
         <v>65</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
+        <v>71</v>
+      </c>
+      <c r="E8" t="n">
         <v>62</v>
       </c>
-      <c r="D8" t="n">
-        <v>64</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>67</v>
       </c>
-      <c r="F8" t="n">
-        <v>63</v>
-      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
@@ -2821,11 +2797,7 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Needs attention — performance has slipped recently.</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2834,19 +2806,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2856,7 +2828,11 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ups and downs need to be understood — talk to student directly.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2865,19 +2841,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2887,11 +2863,7 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2900,10 +2872,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" t="n">
         <v>56</v>
@@ -2919,7 +2891,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
+          <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2931,31 +2903,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
         <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
+          <t>Motion &amp; Time</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -2969,30 +2941,26 @@
         <v>56</v>
       </c>
       <c r="C13" t="n">
+        <v>64</v>
+      </c>
+      <c r="D13" t="n">
+        <v>64</v>
+      </c>
+      <c r="E13" t="n">
+        <v>56</v>
+      </c>
+      <c r="F13" t="n">
         <v>62</v>
       </c>
-      <c r="D13" t="n">
-        <v>60</v>
-      </c>
-      <c r="E13" t="n">
-        <v>61</v>
-      </c>
-      <c r="F13" t="n">
-        <v>61</v>
-      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Heat</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3001,16 +2969,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
         <v>43</v>
@@ -3021,7 +2989,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
+          <t>Struggling with fundamentals, needs remedial sessions.</t>
         </is>
       </c>
     </row>
@@ -3032,26 +3000,26 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Weather &amp; Climate</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -3063,28 +3031,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Acids Bases &amp; Salts</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -3094,24 +3058,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C17" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E17" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Weather &amp; Climate</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -3121,19 +3089,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E18" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3152,33 +3120,29 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C19" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D19" t="n">
+        <v>64</v>
+      </c>
+      <c r="E19" t="n">
+        <v>54</v>
+      </c>
+      <c r="F19" t="n">
         <v>63</v>
       </c>
-      <c r="E19" t="n">
-        <v>67</v>
-      </c>
-      <c r="F19" t="n">
-        <v>70</v>
-      </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Unpredictable performance, may help to identify what's different on good days.</t>
-        </is>
-      </c>
+          <t>Nutrition in Plants</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3187,26 +3151,26 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C20" t="n">
         <v>84</v>
       </c>
       <c r="D20" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E20" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F20" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Motion &amp; Time</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3218,28 +3182,24 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>58</v>
+      </c>
+      <c r="C21" t="n">
         <v>67</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
+        <v>69</v>
+      </c>
+      <c r="E21" t="n">
+        <v>58</v>
+      </c>
+      <c r="F21" t="n">
         <v>68</v>
       </c>
-      <c r="D21" t="n">
-        <v>60</v>
-      </c>
-      <c r="E21" t="n">
-        <v>62</v>
-      </c>
-      <c r="F21" t="n">
-        <v>69</v>
-      </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Acids Bases &amp; Salts</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -3249,33 +3209,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C22" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D22" t="n">
         <v>65</v>
       </c>
       <c r="E22" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F22" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>On track, but should aim higher with focused practice.</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3284,24 +3236,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C23" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E23" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F23" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Heat</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -3311,29 +3267,33 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Motion &amp; Time</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Below expectations — recommend extra classes after school.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3342,26 +3302,26 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
+          <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3373,24 +3333,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C26" t="n">
+        <v>19</v>
+      </c>
+      <c r="D26" t="n">
         <v>20</v>
       </c>
-      <c r="D26" t="n">
-        <v>16</v>
-      </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -3400,26 +3364,26 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C27" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D27" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
         <v>46</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
+          <t>Nutrition in Plants</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3431,29 +3395,33 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C28" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D28" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E28" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F28" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Heat</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Weather &amp; Climate</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Was doing well earlier, something seems to be affecting focus now.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3462,33 +3430,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C29" t="n">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="E29" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="F29" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Ups and downs need to be understood — talk to student directly.</t>
-        </is>
-      </c>
+          <t>Nutrition in Plants</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3497,33 +3461,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C30" t="n">
         <v>79</v>
       </c>
       <c r="D30" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E30" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="F30" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Strong performer, small gains possible with more practice.</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3532,24 +3488,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C31" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E31" t="n">
         <v>64</v>
       </c>
       <c r="F31" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Motion &amp; Time</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
@@ -3631,19 +3591,19 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C2" t="n">
         <v>32</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33</v>
       </c>
       <c r="D2" t="n">
         <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3662,16 +3622,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
         <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
         <v>33</v>
@@ -3684,11 +3644,7 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3706,15 +3662,19 @@
         <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Letter Writing</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -3724,29 +3684,33 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Very low scores across the board, please involve parents.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3755,33 +3719,29 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
         <v>12</v>
       </c>
-      <c r="F6" t="n">
-        <v>13</v>
-      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Serious concern — immediate intervention needed.</t>
-        </is>
-      </c>
+          <t>Letter Writing</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3793,30 +3753,22 @@
         <v>34</v>
       </c>
       <c r="C7" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Great turnaround this term, keep the momentum going!</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3825,28 +3777,24 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" t="n">
         <v>23</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" t="n">
         <v>24</v>
       </c>
-      <c r="D8" t="n">
-        <v>25</v>
-      </c>
-      <c r="E8" t="n">
-        <v>22</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22</v>
-      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -3856,19 +3804,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -3878,11 +3826,7 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Unpredictable performance, may help to identify what's different on good days.</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3891,28 +3835,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
+        <v>42</v>
+      </c>
+      <c r="D10" t="n">
+        <v>43</v>
+      </c>
+      <c r="E10" t="n">
         <v>40</v>
       </c>
-      <c r="D10" t="n">
-        <v>37</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>42</v>
       </c>
-      <c r="F10" t="n">
-        <v>40</v>
-      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -3922,13 +3862,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E11" t="n">
         <v>29</v>
@@ -3939,11 +3879,7 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -3953,26 +3889,26 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>28</v>
+      </c>
+      <c r="C12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" t="n">
         <v>31</v>
       </c>
-      <c r="C12" t="n">
-        <v>32</v>
-      </c>
-      <c r="D12" t="n">
-        <v>29</v>
-      </c>
-      <c r="E12" t="n">
-        <v>27</v>
-      </c>
-      <c r="F12" t="n">
-        <v>28</v>
-      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -3984,25 +3920,33 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
+        <v>33</v>
+      </c>
+      <c r="D13" t="n">
+        <v>33</v>
+      </c>
+      <c r="E13" t="n">
         <v>28</v>
       </c>
-      <c r="D13" t="n">
-        <v>28</v>
-      </c>
-      <c r="E13" t="n">
-        <v>30</v>
-      </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Letter Writing</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Average performance — revision of basics recommended.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4011,26 +3955,26 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
         <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
+          <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -4042,33 +3986,29 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Very low scores across the board, please involve parents.</t>
-        </is>
-      </c>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4077,24 +4017,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Reading Comprehension</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4104,29 +4048,29 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>29</v>
+      </c>
+      <c r="C17" t="n">
         <v>31</v>
       </c>
-      <c r="C17" t="n">
-        <v>35</v>
-      </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Encouraging progress, on the right track now.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4135,19 +4079,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -4166,29 +4110,29 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Ups and downs need to be understood — talk to student directly.</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4197,28 +4141,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" t="n">
         <v>38</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -4228,26 +4168,26 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>32</v>
+      </c>
+      <c r="C21" t="n">
+        <v>32</v>
+      </c>
+      <c r="D21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" t="n">
         <v>33</v>
       </c>
-      <c r="C21" t="n">
-        <v>29</v>
-      </c>
-      <c r="D21" t="n">
-        <v>32</v>
-      </c>
-      <c r="E21" t="n">
-        <v>30</v>
-      </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
+          <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -4259,29 +4199,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E22" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4290,19 +4226,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C23" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D23" t="n">
+        <v>34</v>
+      </c>
+      <c r="E23" t="n">
         <v>32</v>
       </c>
-      <c r="E23" t="n">
-        <v>37</v>
-      </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -4317,19 +4253,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
+        <v>13</v>
+      </c>
+      <c r="F24" t="n">
         <v>17</v>
-      </c>
-      <c r="F24" t="n">
-        <v>18</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -4337,7 +4273,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
+          <t>Below expectations — recommend extra classes after school.</t>
         </is>
       </c>
     </row>
@@ -4348,33 +4284,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Letter Writing</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Very low scores across the board, please involve parents.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4383,29 +4311,29 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Very low scores across the board, please involve parents.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4414,26 +4342,26 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>33</v>
+      </c>
+      <c r="C27" t="n">
+        <v>29</v>
+      </c>
+      <c r="D27" t="n">
         <v>31</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>30</v>
       </c>
-      <c r="D27" t="n">
-        <v>35</v>
-      </c>
-      <c r="E27" t="n">
-        <v>34</v>
-      </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
+          <t>Reading Comprehension</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4445,25 +4373,29 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D28" t="n">
         <v>22</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Noticeable drop in performance, please check in at home.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4472,33 +4404,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Ups and downs need to be understood — talk to student directly.</t>
-        </is>
-      </c>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4507,29 +4435,29 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C30" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D30" t="n">
+        <v>42</v>
+      </c>
+      <c r="E30" t="n">
+        <v>41</v>
+      </c>
+      <c r="F30" t="n">
         <v>43</v>
       </c>
-      <c r="E30" t="n">
-        <v>37</v>
-      </c>
-      <c r="F30" t="n">
-        <v>39</v>
-      </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>The Ant and the Cricket (Poem)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4538,24 +4466,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F31" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
@@ -4637,26 +4569,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4672,31 +4604,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C3" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -4707,24 +4639,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Gadya Pathya 1</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Finding it difficult to keep pace, needs individual attention.</t>
@@ -4738,24 +4674,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Serious concern — immediate intervention needed.</t>
@@ -4769,31 +4709,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Padya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Very low scores across the board, please involve parents.</t>
+          <t>Serious concern — immediate intervention needed.</t>
         </is>
       </c>
     </row>
@@ -4804,16 +4740,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D7" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F7" t="n">
         <v>85</v>
@@ -4821,10 +4757,14 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
+          <t>Great turnaround this term, keep the momentum going!</t>
         </is>
       </c>
     </row>
@@ -4835,26 +4775,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -4870,19 +4810,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="E9" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4894,7 +4834,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ups and downs need to be understood — talk to student directly.</t>
+          <t>Unpredictable performance, may help to identify what's different on good days.</t>
         </is>
       </c>
     </row>
@@ -4905,27 +4845,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C10" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D10" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -4936,16 +4880,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C11" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
         <v>53</v>
@@ -4953,10 +4897,14 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -4967,31 +4915,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C12" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
         <v>58</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -5002,27 +4950,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -5033,31 +4985,31 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>40</v>
+      </c>
+      <c r="C14" t="n">
         <v>35</v>
       </c>
-      <c r="C14" t="n">
-        <v>42</v>
-      </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Gadya Pathya 1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Below expectations — recommend extra classes after school.</t>
         </is>
       </c>
     </row>
@@ -5068,24 +5020,28 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>22</v>
+      </c>
+      <c r="E15" t="n">
         <v>18</v>
       </c>
-      <c r="C15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="n">
-        <v>15</v>
-      </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>Very low scores across the board, please involve parents.</t>
@@ -5099,31 +5055,31 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
         <v>13</v>
       </c>
-      <c r="C16" t="n">
-        <v>19</v>
-      </c>
-      <c r="D16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E16" t="n">
-        <v>19</v>
-      </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
+          <t>Serious concern — immediate intervention needed.</t>
         </is>
       </c>
     </row>
@@ -5134,24 +5090,28 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>77</v>
+      </c>
+      <c r="C17" t="n">
         <v>79</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E17" t="n">
+        <v>80</v>
+      </c>
+      <c r="F17" t="n">
         <v>84</v>
       </c>
-      <c r="D17" t="n">
-        <v>75</v>
-      </c>
-      <c r="E17" t="n">
-        <v>78</v>
-      </c>
-      <c r="F17" t="n">
-        <v>78</v>
-      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -5165,31 +5125,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Gadya Pathya 1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Noticeable drop in performance, please check in at home.</t>
+          <t>Needs attention — performance has slipped recently.</t>
         </is>
       </c>
     </row>
@@ -5200,19 +5160,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" t="n">
+        <v>58</v>
+      </c>
+      <c r="D19" t="n">
+        <v>51</v>
+      </c>
+      <c r="E19" t="n">
         <v>48</v>
       </c>
-      <c r="D19" t="n">
-        <v>49</v>
-      </c>
-      <c r="E19" t="n">
-        <v>46</v>
-      </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -5235,26 +5195,26 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C20" t="n">
+        <v>74</v>
+      </c>
+      <c r="D20" t="n">
         <v>83</v>
       </c>
-      <c r="D20" t="n">
-        <v>73</v>
-      </c>
       <c r="E20" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F20" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -5270,26 +5230,26 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C21" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D21" t="n">
         <v>59</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Gadya Pathya 1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5305,31 +5265,27 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C22" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F22" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Padya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -5340,27 +5296,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C23" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F23" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -5371,31 +5331,27 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Vyakarana Basics</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -5406,26 +5362,26 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
         <v>21</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -5441,19 +5397,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C26" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" t="n">
         <v>15</v>
       </c>
-      <c r="D26" t="n">
-        <v>17</v>
-      </c>
-      <c r="E26" t="n">
-        <v>25</v>
-      </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -5465,7 +5421,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Very low scores across the board, please involve parents.</t>
+          <t>Serious concern — immediate intervention needed.</t>
         </is>
       </c>
     </row>
@@ -5476,27 +5432,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" t="n">
+        <v>80</v>
+      </c>
+      <c r="D27" t="n">
         <v>77</v>
-      </c>
-      <c r="D27" t="n">
-        <v>80</v>
       </c>
       <c r="E27" t="n">
         <v>81</v>
       </c>
       <c r="F27" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Great turnaround this term, keep the momentum going!</t>
+          <t>Encouraging progress, on the right track now.</t>
         </is>
       </c>
     </row>
@@ -5507,24 +5467,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E28" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F28" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Noticeable drop in performance, please check in at home.</t>
@@ -5538,19 +5502,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="C29" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="E29" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="F29" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -5562,7 +5526,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Inconsistent results — strong in some tests, weak in others.</t>
+          <t>Ups and downs need to be understood — talk to student directly.</t>
         </is>
       </c>
     </row>
@@ -5573,19 +5537,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C30" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D30" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="E30" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F30" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -5608,19 +5572,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C31" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D31" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="E31" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F31" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -5628,7 +5592,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>

--- a/samples/Sample_9_For_School_Management_Section_C_Class7.xlsx
+++ b/samples/Sample_9_For_School_Management_Section_C_Class7.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETUP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Test 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mid-Term" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Test 2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Exam" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7C-Unit Test 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7C-Mid-Term" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7C-Unit Test 2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7C-Final Exam" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -637,7 +637,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unit Test 1</t>
+          <t>Class7C-Unit Test 1</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mid-Term</t>
+          <t>Class7C-Mid-Term</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unit Test 2</t>
+          <t>Class7C-Unit Test 2</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Final Exam</t>
+          <t>Class7C-Final Exam</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1698,8 +1697,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1730,7 +1727,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1756,8 +1752,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1788,7 +1782,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1814,8 +1807,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1841,7 +1832,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Inconsistent results — strong in some tests, weak in others.</t>
@@ -1877,7 +1867,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1908,7 +1897,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1939,7 +1927,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1970,7 +1957,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2031,8 +2017,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2058,8 +2042,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2090,7 +2072,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2116,8 +2097,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2143,7 +2122,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Unpredictable performance, may help to identify what's different on good days.</t>
@@ -2174,8 +2152,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2206,7 +2182,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2267,7 +2242,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -2303,7 +2277,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2329,8 +2302,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2361,7 +2332,6 @@
           <t>Perimeter &amp; Area</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2427,7 +2397,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2453,8 +2422,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2480,8 +2447,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2512,7 +2477,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2610,8 +2574,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2637,8 +2599,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2669,7 +2629,6 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2700,7 +2659,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2731,7 +2689,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2797,7 +2754,6 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2863,7 +2819,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2894,7 +2849,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2960,7 +2914,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2986,7 +2939,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Struggling with fundamentals, needs remedial sessions.</t>
@@ -3022,7 +2974,6 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3048,8 +2999,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3080,7 +3029,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3111,7 +3059,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3142,7 +3089,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3173,7 +3119,6 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3199,8 +3144,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3226,8 +3169,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3258,7 +3199,6 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3324,7 +3264,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3355,7 +3294,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3386,7 +3324,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3452,7 +3389,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3478,8 +3414,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3510,7 +3444,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3613,7 +3546,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3644,7 +3576,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3675,7 +3606,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3741,7 +3671,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3767,8 +3696,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3794,8 +3721,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3826,7 +3751,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3852,8 +3776,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3879,8 +3801,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3911,7 +3831,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3977,7 +3896,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4008,7 +3926,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4039,7 +3956,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4065,7 +3981,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Encouraging progress, on the right track now.</t>
@@ -4101,7 +4016,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4132,7 +4046,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4158,8 +4071,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4190,7 +4101,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4216,8 +4126,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4243,8 +4151,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4270,7 +4176,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Below expectations — recommend extra classes after school.</t>
@@ -4301,8 +4206,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4333,7 +4236,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4364,7 +4266,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4390,7 +4291,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Noticeable drop in performance, please check in at home.</t>
@@ -4426,7 +4326,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4452,7 +4351,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -4488,7 +4386,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4726,7 +4623,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Serious concern — immediate intervention needed.</t>
@@ -5282,7 +5178,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -5348,7 +5243,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Finding it difficult to keep pace, needs individual attention.</t>
@@ -5589,7 +5483,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
